--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-architecture-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-architecture-hard.xlsx
@@ -463,13 +463,13 @@
         <v>Thiết kế kiến trúc hướng sự kiện (Event-driven): Sử dụng ngắt DMA để nhận/gửi dữ liệu UART và SPI vào các bộ đệm vòng (Ring Buffers); xử lý ghi Flash và truyền 4G ở luồng chính (background task) để không chặn việc lấy mẫu cảm biến — DMA Ring Buffers kết hợp xử lý tầng nền</v>
       </c>
       <c r="G2" t="str">
-        <v>Sử dụng kiến trúc Super Loop (Bare-metal) chạy tuần tự: Đọc cảm biến -&gt; Ghi Flash -&gt; Gửi 4G UART; dùng hàm delay_ms() để chờ phản hồi từ modem 4G — Super Loop tuần tự rủi ro mất mát dữ liệu</v>
+        <v>Thiết kế để cảm biến SPI tự động gửi dữ liệu trực tiếp vào modem 4G UART mà không đi qua vi điều khiển trung gian — truyền trực tiếp ngoại vi không hỗ trợ</v>
       </c>
       <c r="H2" t="str">
         <v>Sử dụng hệ điều hành RTOS và đưa tất cả các tác vụ đọc cảm biến, ghi Flash và truyền 4G vào chung một Task có độ ưu tiên cao nhất — chung một task không tối ưu đa nhiệm</v>
       </c>
       <c r="I2" t="str">
-        <v>Thiết kế để cảm biến SPI tự động gửi dữ liệu trực tiếp vào modem 4G UART mà không đi qua vi điều khiển trung gian — truyền trực tiếp ngoại vi không hỗ trợ</v>
+        <v>Sử dụng kiến trúc Super Loop (Bare-metal) chạy tuần tự: Đọc cảm biến -&gt; Ghi Flash -&gt; Gửi 4G UART; dùng hàm delay_ms() để chờ phản hồi từ modem 4G — Super Loop tuần tự rủi ro mất mát dữ liệu</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -492,19 +492,19 @@
         <v>Nếu không tắt các ngắt ngoại vi và SysTick của Bootloader trước khi Jump, khi sang chương trình Application, một ngắt cũ xảy ra sẽ nhảy vào địa chỉ xử lý ngắt (ISR vector table) của Bootloader cũ, gây lỗi nhảy vùng nhớ bậy (HardFault). Cấu hình lại MSP (Main Stack Pointer) về địa chỉ đỉnh stack của ứng dụng mới là bắt buộc để ứng dụng chạy đúng vùng nhớ RAM cấp phát của nó.</v>
       </c>
       <c r="F3" t="str">
+        <v>Chỉ cần gọi trực tiếp con trỏ hàm trỏ đến địa chỉ Flash của ứng dụng mới mà không cần tắt ngắt hay cấu hình lại MSP — jump trực tiếp rủi ro sập ngắt</v>
+      </c>
+      <c r="G3" t="str">
         <v>Tắt toàn bộ các ngắt ngoại vi, reset lại cấu hình NVIC, tắt ngắt hệ thống SysTick, thiết lập con trỏ Stack Pointer (MSP) về địa chỉ bắt đầu của ứng dụng mới, và gọi con trỏ hàm trỏ đến Vector Reset của ứng dụng mới — de-initialize ngoại vi cấu hình Stack Pointer và jump Vector Reset</v>
       </c>
-      <c r="G3" t="str">
-        <v>Chỉ cần gọi trực tiếp con trỏ hàm trỏ đến địa chỉ Flash của ứng dụng mới mà không cần tắt ngắt hay cấu hình lại MSP — jump trực tiếp rủi ro sập ngắt</v>
-      </c>
       <c r="H3" t="str">
+        <v>Gửi một bản tin UART báo cáo trạng thái thành công về máy tính và tắt nguồn điện của chip — tắt nguồn chip</v>
+      </c>
+      <c r="I3" t="str">
         <v>Thực hiện xóa bỏ phân vùng bộ nhớ của Bootloader trên Flash để nhường chỗ cho ứng dụng mới chạy — xóa bộ nhớ Bootloader nguy hiểm</v>
       </c>
-      <c r="I3" t="str">
-        <v>Gửi một bản tin UART báo cáo trạng thái thành công về máy tính và tắt nguồn điện của chip — tắt nguồn chip</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -527,13 +527,13 @@
         <v>Harvard có đường bus độc lập cho bộ nhớ chương trình (Code) và bộ nhớ dữ liệu (Data), cho phép CPU đọc lệnh và truy xuất dữ liệu song song; Von Neumann sử dụng chung một đường bus chung cho cả hai, gây nghẽn cổ chai bus (bus bottleneck) — bus độc lập song song vs bus dùng chung nghẽn cổ chai</v>
       </c>
       <c r="G4" t="str">
+        <v>Harvard bắt buộc sử dụng bộ nhớ ngoài Flash dạng thẻ nhớ SD; còn Von Neumann chỉ hỗ trợ RAM tĩnh SRAM — phân loại công nghệ bộ nhớ</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Harvard tiêu thụ điện năng nhiều gấp 10 lần so với Von Neumann do kiến trúc bus phức tạp — so sánh tiêu thụ điện năng</v>
+      </c>
+      <c r="I4" t="str">
         <v>Harvard chỉ chạy được trên các dòng vi điều khiển 8-bit; còn Von Neumann chỉ chạy trên các dòng vi xử lý 64-bit — phân loại theo số bit</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Harvard bắt buộc sử dụng bộ nhớ ngoài Flash dạng thẻ nhớ SD; còn Von Neumann chỉ hỗ trợ RAM tĩnh SRAM — phân loại công nghệ bộ nhớ</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Harvard tiêu thụ điện năng nhiều gấp 10 lần so với Von Neumann do kiến trúc bus phức tạp — so sánh tiêu thụ điện năng</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -559,13 +559,13 @@
         <v>HSM cho phép các trạng thái con kế thừa các hành vi chuyển trạng thái (Transitions) của trạng thái cha, giúp nhóm các logic xử lý chung và giảm thiểu số lượng đường nối chuyển trạng thái chéo chằng chịt — kế thừa trạng thái giảm bùng nổ trạng thái</v>
       </c>
       <c r="G5" t="str">
-        <v>HSM sử dụng trí tuệ nhân tạo AI để tự động dự báo các trạng thái tiếp theo của hệ thống — tự động dự báo trạng thái</v>
+        <v>HSM tự động xóa bỏ hoàn toàn các trạng thái lỗi hệ thống để đơn giản hóa sơ đồ — xóa bỏ trạng thái lỗi</v>
       </c>
       <c r="H5" t="str">
         <v>HSM bắt buộc toàn bộ dữ liệu trạng thái phải được lưu trên một máy chủ cơ sở dữ liệu bên ngoài chip — lưu trữ cơ sở dữ liệu ngoài</v>
       </c>
       <c r="I5" t="str">
-        <v>HSM tự động xóa bỏ hoàn toàn các trạng thái lỗi hệ thống để đơn giản hóa sơ đồ — xóa bỏ trạng thái lỗi</v>
+        <v>HSM sử dụng trí tuệ nhân tạo AI để tự động dự báo các trạng thái tiếp theo của hệ thống — tự động dự báo trạng thái</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Lỗi lớn nhất của người mới học là viết code quá nặng (như `printf`, ghi Flash, delay) trong ISR. Vì khi ISR đang chạy, các ngắt có độ ưu tiên thấp hơn sẽ bị chặn hoàn toàn, gây mất mát dữ liệu ngoại vi khác và tăng vọt độ trễ ngắt toàn hệ thống. Quy tắc vàng: ISR là người phát tin báo (nhanh nhất có thể), chương trình chính là người xử lý tin.</v>
       </c>
       <c r="F6" t="str">
-        <v>Giữ cho các chương trình phục vụ ngắt (ISR) cực kỳ ngắn gọn (chỉ xóa cờ ngắt, đọc dữ liệu thô và đẩy vào buffer/queue), tuyệt đối không gọi các hàm block/delay, không gọi API IO nặng; xử lý logic chạy ở ngoài ISR — tối giản hóa ISR xử lý logic ở background</v>
+        <v>Yêu cầu vi điều khiển phải chạy ở chế độ xung nhịp thấp nhất để giảm thiểu nhiễu tín hiệu ngắt — giảm xung nhịp chip</v>
       </c>
       <c r="G6" t="str">
         <v>Đưa toàn bộ thuật toán điều khiển phanh phức tạp và việc gửi dữ liệu hiển thị LCD vào chạy trực tiếp trong ISR của ngắt — chạy thuật toán nặng trong ISR</v>
       </c>
       <c r="H6" t="str">
+        <v>Giữ cho các chương trình phục vụ ngắt (ISR) cực kỳ ngắn gọn (chỉ xóa cờ ngắt, đọc dữ liệu thô và đẩy vào buffer/queue), tuyệt đối không gọi các hàm block/delay, không gọi API IO nặng; xử lý logic chạy ở ngoài ISR — tối giản hóa ISR xử lý logic ở background</v>
+      </c>
+      <c r="I6" t="str">
         <v>Tắt toàn bộ các ngắt của vi điều khiển và chuyển sang sử dụng cơ chế Polling quét tuần tự trong Super Loop — tắt ngắt chuyển Polling</v>
       </c>
-      <c r="I6" t="str">
-        <v>Yêu cầu vi điều khiển phải chạy ở chế độ xung nhịp thấp nhất để giảm thiểu nhiễu tín hiệu ngắt — giảm xung nhịp chip</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Trong AUTOSAR, RTE là lớp cốt lõi. Nó che giấu việc triển khai thực tế của các liên kết. Một Component A gửi dữ liệu cho Component B thông qua các cổng RTE (RTE ports). Việc 2 component này nằm trên cùng 1 chip hay nằm ở 2 ECU khác nhau giao tiếp qua mạng CAN hoàn toàn do RTE xử lý cấu hình, giúp tăng khả năng tái sử dụng phần mềm xe hơi cực cao.</v>
       </c>
       <c r="F7" t="str">
+        <v>Là hệ thống điều hòa tự động điều chỉnh nhiệt độ cho con chip vi điều khiển trên mạch — điều hòa nhiệt độ chip</v>
+      </c>
+      <c r="G7" t="str">
         <v>Đóng vai trò là cầu nối giao tiếp trung gian (trừu tượng hóa hoàn toàn) giữa các thành phần ứng dụng phần mềm (Software Components - SWCs) với nhau và giữa SWCs với tầng dịch vụ phần mềm cơ sở (BSW) — trừu tượng hóa giao tiếp ứng dụng và bsw</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Đóng vai trò tự động nạp lại chương trình ứng dụng mới cho hộp ECU thông qua cổng giao tiếp OBD-II — nạp chương trình tự động</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>Chịu trách nhiệm mã hóa toàn bộ dữ liệu truyền thông trên mạng CAN bus của xe ô tô — mã hóa CAN bus</v>
       </c>
-      <c r="I7" t="str">
-        <v>Là hệ thống điều hòa tự động điều chỉnh nhiệt độ cho con chip vi điều khiển trên mạch — điều hòa nhiệt độ chip</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Cảm biến gia tốc đo trọng lực rất tốt ở trạng thái tĩnh nhưng bị nhiễu cực mạnh khi drone rung động do động cơ quay. Cảm biến con quay đo tốc độ góc rất nhanh nhưng khi tích phân tính góc sẽ bị lỗi tích lũy (drift) làm sai góc sau vài phút. Lọc Kalman/Bù kết hợp điểm mạnh của cả hai cảm biến để ước lượng góc nghiêng chính xác, giúp drone giữ thăng bằng ổn định.</v>
       </c>
       <c r="F8" t="str">
-        <v>Để kết hợp và lọc nhiễu tín hiệu từ cảm biến gia tốc (Accelerometer - nhạy với nhiễu động) và cảm biến con quay hồi chuyển (Gyroscope - bị trôi góc theo thời gian) nhằm tính toán chính xác góc nghiêng của drone — lọc kết hợp cảm biến IMU</v>
+        <v>Để đảm bảo pin của thiết bị drone tự động sạc đầy trong vòng 5 phút khi đang bay — sạc pin drone</v>
       </c>
       <c r="G8" t="str">
         <v>Để tự động điều chỉnh tốc độ quay của quạt tản nhiệt máy bay theo nhiệt độ môi trường — tản nhiệt drone</v>
       </c>
       <c r="H8" t="str">
+        <v>Để kết hợp và lọc nhiễu tín hiệu từ cảm biến gia tốc (Accelerometer - nhạy với nhiễu động) và cảm biến con quay hồi chuyển (Gyroscope - bị trôi góc theo thời gian) nhằm tính toán chính xác góc nghiêng của drone — lọc kết hợp cảm biến IMU</v>
+      </c>
+      <c r="I8" t="str">
         <v>Để mã hóa toàn bộ hình ảnh camera gửi từ máy bay về điện thoại của người điều khiển — mã hóa hình ảnh camera</v>
       </c>
-      <c r="I8" t="str">
-        <v>Để đảm bảo pin của thiết bị drone tự động sạc đầy trong vòng 5 phút khi đang bay — sạc pin drone</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         <v>ARM TrustZone mang lại bảo mật ở tầng phần cứng (hardware-enforced isolation). Ngay cả khi hacker khai thác thành công lỗi tràn bộ đệm ở tầng ứng dụng (Non-secure World) để chiếm quyền root, hacker vẫn không thể truy cập vào vùng nhớ RAM, thanh ghi ngoại vi hoặc bộ nhớ Flash thuộc phân vùng Secure World, bảo vệ an toàn cho các dữ liệu nhạy cảm.</v>
       </c>
       <c r="F9" t="str">
-        <v>Nó chia tách bộ xử lý vật lý thành hai phân vùng ảo độc lập: Phân vùng bảo mật (Secure World) chứa key, mật mã, bootloader an toàn và Phân vùng thông thường (Non-secure World) chạy OS/Application — ARM TrustZone phân vùng bảo mật phần cứng</v>
+        <v>Nó bắt buộc toàn bộ mã nguồn chương trình phải được lưu trên máy chủ Cloud của ARM — lưu trữ đám mây ARM</v>
       </c>
       <c r="G9" t="str">
         <v>Nó tự động ngắt kết nối nguồn điện của chip nếu phát hiện có thiết bị ngoại vi lạ cắm vào — ngắt nguồn chip</v>
@@ -693,10 +693,10 @@
         <v>Nó yêu cầu lập trình viên phải quét dấu vân tay mỗi khi muốn nạp code mới vào chip — quét vân tay nạp code</v>
       </c>
       <c r="I9" t="str">
-        <v>Nó bắt buộc toàn bộ mã nguồn chương trình phải được lưu trên máy chủ Cloud của ARM — lưu trữ đám mây ARM</v>
+        <v>Nó chia tách bộ xử lý vật lý thành hai phân vùng ảo độc lập: Phân vùng bảo mật (Secure World) chứa key, mật mã, bootloader an toàn và Phân vùng thông thường (Non-secure World) chạy OS/Application — ARM TrustZone phân vùng bảo mật phần cứng</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Một hàm không đạt Reentrant (ví dụ sử dụng biến toàn cục hoặc static để lưu trạng thái trung gian). Nếu Task A đang gọi hàm này nửa chừng, ngắt xảy ra, ISR cũng gọi hàm này và sửa biến toàn cục đó. Khi quay lại Task A, dữ liệu của Task A đã bị hỏng hoàn toàn. Hàm Reentrant chỉ làm việc trên dữ liệu stack cục bộ (local variables) hoặc dữ liệu truyền vào qua con trỏ riêng biệt.</v>
       </c>
       <c r="F10" t="str">
+        <v>Là hàm tự động gọi lại chính nó (đệ quy) liên tục cho đến khi bộ nhớ RAM bị tràn — hàm đệ quy tràn bộ nhớ</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Là hàm tự động reset lại vi điều khiển khi có lỗi logic toán học xảy ra trong code — tự động reset chip</v>
+      </c>
+      <c r="H10" t="str">
         <v>Là hàm có thể được gọi đồng thời bởi nhiều luồng (tasks) hoặc ngắt (ISR) khác nhau mà không làm hỏng dữ liệu, vì nó không sử dụng biến tĩnh (static) hoặc biến toàn cục không được bảo vệ — hàm an toàn đa nhiệm</v>
       </c>
-      <c r="G10" t="str">
-        <v>Là hàm tự động gọi lại chính nó (đệ quy) liên tục cho đến khi bộ nhớ RAM bị tràn — hàm đệ quy tràn bộ nhớ</v>
-      </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Là hàm bắt buộc phải được biên dịch bằng 2 trình biên dịch khác nhau cùng một lúc — biên dịch chéo</v>
       </c>
-      <c r="I10" t="str">
-        <v>Là hàm tự động reset lại vi điều khiển khi có lỗi logic toán học xảy ra trong code — tự động reset chip</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Mặc định khi bật nguồn, MCU đọc vector ngắt ở địa chỉ `0x00000000` (hoặc `0x08000000` trên STM32 Flash). Khi Bootloader nhảy sang Application mới nằm ở địa chỉ khác (ví dụ `0x08010000`), ta phải cập nhật lại thanh ghi `VTOR` trỏ đến địa chỉ mới này để khi ngoại vi của Application phát sinh ngắt, MCU sẽ gọi đúng ISR được định nghĩa trong code của Application mới, tránh HardFault.</v>
       </c>
       <c r="F11" t="str">
+        <v>Thiết lập cấu hình cho vi điều khiển tự động reset lại chip sau mỗi ngắt ngoại vi xảy ra — reset chip sau mỗi ngắt</v>
+      </c>
+      <c r="G11" t="str">
         <v>Gọi câu lệnh ghi vào thanh ghi Vector Table Offset Register (VTOR) trên nhân ARM Cortex-M (ví dụ `SCB-&gt;VTOR = ApplicationAddress;`) để dịch chuyển địa chỉ bảng vector ngắt về phân vùng của Application — dịch chuyển địa chỉ bảng vector ngắt VTOR</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Yêu cầu lập trình viên copy thủ công bảng vector ngắt của ứng dụng đè lên vùng nhớ RAM của hệ thống — copy vector ngắt lên RAM</v>
       </c>
       <c r="H11" t="str">
         <v>Tắt toàn bộ bảng vector ngắt và cấm sử dụng ngắt trong chương trình Application mới — cấm ngắt ở Application</v>
       </c>
       <c r="I11" t="str">
-        <v>Thiết lập cấu hình cho vi điều khiển tự động reset lại chip sau mỗi ngắt ngoại vi xảy ra — reset chip sau mỗi ngắt</v>
+        <v>Yêu cầu lập trình viên copy thủ công bảng vector ngắt của ứng dụng đè lên vùng nhớ RAM của hệ thống — copy vector ngắt lên RAM</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
